--- a/output/yearly_total_coral_cover_iteration_7_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_7_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.253963207961447</v>
+        <v>1.292928774343003</v>
       </c>
       <c r="C3" t="n">
-        <v>4.587232728864356</v>
+        <v>4.72961559841127</v>
       </c>
       <c r="D3" t="n">
-        <v>6.09004126651923</v>
+        <v>6.060382668373934</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93123720334503</v>
+        <v>12.08292704112821</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.377961115996284</v>
+        <v>1.479663803044465</v>
       </c>
       <c r="C4" t="n">
-        <v>5.015318228970311</v>
+        <v>5.384770799366199</v>
       </c>
       <c r="D4" t="n">
-        <v>6.317552790874492</v>
+        <v>6.272183169453498</v>
       </c>
       <c r="E4" t="n">
-        <v>12.71083213584109</v>
+        <v>13.13661777186416</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.561145893704244</v>
+        <v>1.722915622045563</v>
       </c>
       <c r="C5" t="n">
-        <v>5.548200707619522</v>
+        <v>6.243927222824459</v>
       </c>
       <c r="D5" t="n">
-        <v>6.63087128755272</v>
+        <v>6.508080442270984</v>
       </c>
       <c r="E5" t="n">
-        <v>13.74021788887649</v>
+        <v>14.474923287141</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.776982647369953</v>
+        <v>1.993724803994784</v>
       </c>
       <c r="C6" t="n">
-        <v>6.189490188172556</v>
+        <v>7.250513618473583</v>
       </c>
       <c r="D6" t="n">
-        <v>6.987299569722662</v>
+        <v>6.774039870270758</v>
       </c>
       <c r="E6" t="n">
-        <v>14.95377240526517</v>
+        <v>16.01827829273913</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.024339979366803</v>
+        <v>2.284840908256313</v>
       </c>
       <c r="C7" t="n">
-        <v>6.932078026435335</v>
+        <v>8.380180545126947</v>
       </c>
       <c r="D7" t="n">
-        <v>7.460769059321007</v>
+        <v>7.161152408680008</v>
       </c>
       <c r="E7" t="n">
-        <v>16.41718706512314</v>
+        <v>17.82617386206327</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.264892380922819</v>
+        <v>1.447229082388113</v>
       </c>
       <c r="C8" t="n">
-        <v>4.536144252290108</v>
+        <v>5.847343062361294</v>
       </c>
       <c r="D8" t="n">
-        <v>5.813801028272783</v>
+        <v>5.433953563452346</v>
       </c>
       <c r="E8" t="n">
-        <v>11.61483766148571</v>
+        <v>12.72852570820175</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.608702852681373</v>
+        <v>1.801995939682404</v>
       </c>
       <c r="C9" t="n">
-        <v>5.425541308026327</v>
+        <v>7.100223152929716</v>
       </c>
       <c r="D9" t="n">
-        <v>6.387097029713647</v>
+        <v>5.854569961493291</v>
       </c>
       <c r="E9" t="n">
-        <v>13.42134119042135</v>
+        <v>14.75678905410541</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.98147966547236</v>
+        <v>2.178752905324691</v>
       </c>
       <c r="C10" t="n">
-        <v>6.473850661025946</v>
+        <v>8.445201603033277</v>
       </c>
       <c r="D10" t="n">
-        <v>6.957526809309573</v>
+        <v>6.30485817323364</v>
       </c>
       <c r="E10" t="n">
-        <v>15.41285713580788</v>
+        <v>16.92881268159161</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.368922253545884</v>
+        <v>2.558482191311244</v>
       </c>
       <c r="C11" t="n">
-        <v>7.653680476323044</v>
+        <v>9.93702082268365</v>
       </c>
       <c r="D11" t="n">
-        <v>7.531195204170726</v>
+        <v>6.718049039434554</v>
       </c>
       <c r="E11" t="n">
-        <v>17.55379793403965</v>
+        <v>19.21355205342945</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.761446826418072</v>
+        <v>2.945387765756201</v>
       </c>
       <c r="C12" t="n">
-        <v>8.97296545516244</v>
+        <v>11.47579694559046</v>
       </c>
       <c r="D12" t="n">
-        <v>8.093951010799161</v>
+        <v>7.196065383429653</v>
       </c>
       <c r="E12" t="n">
-        <v>19.82836329237967</v>
+        <v>21.61725009477631</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.150276975334391</v>
+        <v>3.312081271795346</v>
       </c>
       <c r="C13" t="n">
-        <v>10.34883606609608</v>
+        <v>13.04337412557588</v>
       </c>
       <c r="D13" t="n">
-        <v>8.597485377223748</v>
+        <v>7.668343304805279</v>
       </c>
       <c r="E13" t="n">
-        <v>22.09659841865422</v>
+        <v>24.02379870217651</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.814151947723596</v>
+        <v>1.917353266394021</v>
       </c>
       <c r="C14" t="n">
-        <v>7.376007946684881</v>
+        <v>9.268513178684413</v>
       </c>
       <c r="D14" t="n">
-        <v>6.54159112041439</v>
+        <v>5.857204978306895</v>
       </c>
       <c r="E14" t="n">
-        <v>15.73175101482287</v>
+        <v>17.04307142338533</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.88429782119203</v>
+        <v>1.960451990610456</v>
       </c>
       <c r="C15" t="n">
-        <v>7.964555877903801</v>
+        <v>9.857925047883073</v>
       </c>
       <c r="D15" t="n">
-        <v>6.591287189203363</v>
+        <v>5.851432301805923</v>
       </c>
       <c r="E15" t="n">
-        <v>16.44014088829919</v>
+        <v>17.66980934029945</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.211700863081299</v>
+        <v>2.273187721798277</v>
       </c>
       <c r="C16" t="n">
-        <v>9.445227765448841</v>
+        <v>11.52058350736434</v>
       </c>
       <c r="D16" t="n">
-        <v>7.117621768404162</v>
+        <v>6.333735496471255</v>
       </c>
       <c r="E16" t="n">
-        <v>18.7745503969343</v>
+        <v>20.12750672563388</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.784719151550277</v>
+        <v>1.816979381111827</v>
       </c>
       <c r="C17" t="n">
-        <v>8.786995382182482</v>
+        <v>10.4276332406575</v>
       </c>
       <c r="D17" t="n">
-        <v>6.645263677982852</v>
+        <v>5.877929672343546</v>
       </c>
       <c r="E17" t="n">
-        <v>17.21697821171561</v>
+        <v>18.12254229411287</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.05386528466954</v>
+        <v>2.086253141432642</v>
       </c>
       <c r="C18" t="n">
-        <v>10.32816256326321</v>
+        <v>12.0888190785824</v>
       </c>
       <c r="D18" t="n">
-        <v>7.088306781955353</v>
+        <v>6.286631241621493</v>
       </c>
       <c r="E18" t="n">
-        <v>19.4703346298881</v>
+        <v>20.46170346163653</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.077446864525548</v>
+        <v>2.104817990519949</v>
       </c>
       <c r="C19" t="n">
-        <v>11.14175652072663</v>
+        <v>12.84426411952327</v>
       </c>
       <c r="D19" t="n">
-        <v>7.200913243632463</v>
+        <v>6.389076614559648</v>
       </c>
       <c r="E19" t="n">
-        <v>20.42011662888464</v>
+        <v>21.33815872460287</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.333869547397772</v>
+        <v>2.358354335141688</v>
       </c>
       <c r="C20" t="n">
-        <v>12.92000595490592</v>
+        <v>14.71254963565904</v>
       </c>
       <c r="D20" t="n">
-        <v>7.674086184648298</v>
+        <v>6.8254045642351</v>
       </c>
       <c r="E20" t="n">
-        <v>22.92796168695198</v>
+        <v>23.89630853503583</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.397694571582099</v>
+        <v>1.410418021829138</v>
       </c>
       <c r="C21" t="n">
-        <v>9.609896307882158</v>
+        <v>10.82560430752803</v>
       </c>
       <c r="D21" t="n">
-        <v>6.391236459508991</v>
+        <v>5.717237208112428</v>
       </c>
       <c r="E21" t="n">
-        <v>17.39882733897325</v>
+        <v>17.95325953746959</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_7_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_7_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.292928774343003</v>
+        <v>1.263348716014047</v>
       </c>
       <c r="C3" t="n">
-        <v>4.72961559841127</v>
+        <v>4.589824542803567</v>
       </c>
       <c r="D3" t="n">
-        <v>6.060382668373934</v>
+        <v>6.113131972523115</v>
       </c>
       <c r="E3" t="n">
-        <v>12.08292704112821</v>
+        <v>11.96630523134073</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.479663803044465</v>
+        <v>1.39705989821598</v>
       </c>
       <c r="C4" t="n">
-        <v>5.384770799366199</v>
+        <v>5.021913467071607</v>
       </c>
       <c r="D4" t="n">
-        <v>6.272183169453498</v>
+        <v>6.386883104559586</v>
       </c>
       <c r="E4" t="n">
-        <v>13.13661777186416</v>
+        <v>12.80585646984717</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.722915622045563</v>
+        <v>1.578389763878699</v>
       </c>
       <c r="C5" t="n">
-        <v>6.243927222824459</v>
+        <v>5.546234781837827</v>
       </c>
       <c r="D5" t="n">
-        <v>6.508080442270984</v>
+        <v>6.753741551912409</v>
       </c>
       <c r="E5" t="n">
-        <v>14.474923287141</v>
+        <v>13.87836609762894</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.993724803994784</v>
+        <v>1.798349956212687</v>
       </c>
       <c r="C6" t="n">
-        <v>7.250513618473583</v>
+        <v>6.197316512604862</v>
       </c>
       <c r="D6" t="n">
-        <v>6.774039870270758</v>
+        <v>7.095128227214994</v>
       </c>
       <c r="E6" t="n">
-        <v>16.01827829273913</v>
+        <v>15.09079469603254</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.284840908256313</v>
+        <v>2.048964154862028</v>
       </c>
       <c r="C7" t="n">
-        <v>8.380180545126947</v>
+        <v>6.942146604156552</v>
       </c>
       <c r="D7" t="n">
-        <v>7.161152408680008</v>
+        <v>7.525305686126209</v>
       </c>
       <c r="E7" t="n">
-        <v>17.82617386206327</v>
+        <v>16.51641644514479</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.447229082388113</v>
+        <v>1.287205660737413</v>
       </c>
       <c r="C8" t="n">
-        <v>5.847343062361294</v>
+        <v>4.580899702090495</v>
       </c>
       <c r="D8" t="n">
-        <v>5.433953563452346</v>
+        <v>5.836497651067768</v>
       </c>
       <c r="E8" t="n">
-        <v>12.72852570820175</v>
+        <v>11.70460301389568</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.801995939682404</v>
+        <v>1.646528256480973</v>
       </c>
       <c r="C9" t="n">
-        <v>7.100223152929716</v>
+        <v>5.542097400108328</v>
       </c>
       <c r="D9" t="n">
-        <v>5.854569961493291</v>
+        <v>6.360192292723993</v>
       </c>
       <c r="E9" t="n">
-        <v>14.75678905410541</v>
+        <v>13.54881794931329</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.178752905324691</v>
+        <v>2.035226504294814</v>
       </c>
       <c r="C10" t="n">
-        <v>8.445201603033277</v>
+        <v>6.649773810642726</v>
       </c>
       <c r="D10" t="n">
-        <v>6.30485817323364</v>
+        <v>6.912136764957184</v>
       </c>
       <c r="E10" t="n">
-        <v>16.92881268159161</v>
+        <v>15.59713707989472</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.558482191311244</v>
+        <v>2.444466844301264</v>
       </c>
       <c r="C11" t="n">
-        <v>9.93702082268365</v>
+        <v>7.854419085424041</v>
       </c>
       <c r="D11" t="n">
-        <v>6.718049039434554</v>
+        <v>7.561814908093971</v>
       </c>
       <c r="E11" t="n">
-        <v>19.21355205342945</v>
+        <v>17.86070083781928</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.945387765756201</v>
+        <v>2.864464243666804</v>
       </c>
       <c r="C12" t="n">
-        <v>11.47579694559046</v>
+        <v>9.174636975733472</v>
       </c>
       <c r="D12" t="n">
-        <v>7.196065383429653</v>
+        <v>8.064641767022254</v>
       </c>
       <c r="E12" t="n">
-        <v>21.61725009477631</v>
+        <v>20.10374298642253</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.312081271795346</v>
+        <v>3.280603587597344</v>
       </c>
       <c r="C13" t="n">
-        <v>13.04337412557588</v>
+        <v>10.51705597110643</v>
       </c>
       <c r="D13" t="n">
-        <v>7.668343304805279</v>
+        <v>8.653072615643593</v>
       </c>
       <c r="E13" t="n">
-        <v>24.02379870217651</v>
+        <v>22.45073217434737</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.917353266394021</v>
+        <v>1.885181394125853</v>
       </c>
       <c r="C14" t="n">
-        <v>9.268513178684413</v>
+        <v>7.435128793434624</v>
       </c>
       <c r="D14" t="n">
-        <v>5.857204978306895</v>
+        <v>6.582098030691613</v>
       </c>
       <c r="E14" t="n">
-        <v>17.04307142338533</v>
+        <v>15.90240821825209</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.960451990610456</v>
+        <v>1.963367781292069</v>
       </c>
       <c r="C15" t="n">
-        <v>9.857925047883073</v>
+        <v>7.958930463558466</v>
       </c>
       <c r="D15" t="n">
-        <v>5.851432301805923</v>
+        <v>6.65401105002769</v>
       </c>
       <c r="E15" t="n">
-        <v>17.66980934029945</v>
+        <v>16.57630929487823</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.273187721798277</v>
+        <v>2.311171540475586</v>
       </c>
       <c r="C16" t="n">
-        <v>11.52058350736434</v>
+        <v>9.329293179054336</v>
       </c>
       <c r="D16" t="n">
-        <v>6.333735496471255</v>
+        <v>7.222344796016171</v>
       </c>
       <c r="E16" t="n">
-        <v>20.12750672563388</v>
+        <v>18.86280951554609</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.816979381111827</v>
+        <v>1.874450891718435</v>
       </c>
       <c r="C17" t="n">
-        <v>10.4276332406575</v>
+        <v>8.583429995706906</v>
       </c>
       <c r="D17" t="n">
-        <v>5.877929672343546</v>
+        <v>6.775472875997108</v>
       </c>
       <c r="E17" t="n">
-        <v>18.12254229411287</v>
+        <v>17.23335376342245</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.086253141432642</v>
+        <v>2.168818123359799</v>
       </c>
       <c r="C18" t="n">
-        <v>12.0888190785824</v>
+        <v>9.932881485102317</v>
       </c>
       <c r="D18" t="n">
-        <v>6.286631241621493</v>
+        <v>7.24529805734146</v>
       </c>
       <c r="E18" t="n">
-        <v>20.46170346163653</v>
+        <v>19.34699766580358</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.104817990519949</v>
+        <v>2.209599922994212</v>
       </c>
       <c r="C19" t="n">
-        <v>12.84426411952327</v>
+        <v>10.53930704201557</v>
       </c>
       <c r="D19" t="n">
-        <v>6.389076614559648</v>
+        <v>7.381456646443451</v>
       </c>
       <c r="E19" t="n">
-        <v>21.33815872460287</v>
+        <v>20.13036361145323</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.358354335141688</v>
+        <v>2.499107503499553</v>
       </c>
       <c r="C20" t="n">
-        <v>14.71254963565904</v>
+        <v>12.05380013797191</v>
       </c>
       <c r="D20" t="n">
-        <v>6.8254045642351</v>
+        <v>7.951616443161829</v>
       </c>
       <c r="E20" t="n">
-        <v>23.89630853503583</v>
+        <v>22.5045240846333</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.410418021829138</v>
+        <v>1.503409164375396</v>
       </c>
       <c r="C21" t="n">
-        <v>10.82560430752803</v>
+        <v>8.820679145915189</v>
       </c>
       <c r="D21" t="n">
-        <v>5.717237208112428</v>
+        <v>6.6660570943588</v>
       </c>
       <c r="E21" t="n">
-        <v>17.95325953746959</v>
+        <v>16.99014540464939</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_7_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_7_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.263348716014047</v>
+        <v>2.602710860612249</v>
       </c>
       <c r="C3" t="n">
-        <v>4.589824542803567</v>
+        <v>7.756775963133511</v>
       </c>
       <c r="D3" t="n">
-        <v>6.113131972523115</v>
+        <v>8.19756168308716</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96630523134073</v>
+        <v>18.55704850683292</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.39705989821598</v>
+        <v>1.102741794026387</v>
       </c>
       <c r="C4" t="n">
-        <v>5.021913467071607</v>
+        <v>4.580095513855169</v>
       </c>
       <c r="D4" t="n">
-        <v>6.386883104559586</v>
+        <v>5.72285238399613</v>
       </c>
       <c r="E4" t="n">
-        <v>12.80585646984717</v>
+        <v>11.40568969187769</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.578389763878699</v>
+        <v>1.237922198230601</v>
       </c>
       <c r="C5" t="n">
-        <v>5.546234781837827</v>
+        <v>5.300212272790467</v>
       </c>
       <c r="D5" t="n">
-        <v>6.753741551912409</v>
+        <v>6.019802286822622</v>
       </c>
       <c r="E5" t="n">
-        <v>13.87836609762894</v>
+        <v>12.55793675784369</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.798349956212687</v>
+        <v>1.388596483858041</v>
       </c>
       <c r="C6" t="n">
-        <v>6.197316512604862</v>
+        <v>6.201568965037956</v>
       </c>
       <c r="D6" t="n">
-        <v>7.095128227214994</v>
+        <v>6.366128714221929</v>
       </c>
       <c r="E6" t="n">
-        <v>15.09079469603254</v>
+        <v>13.95629416311793</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.048964154862028</v>
+        <v>1.549339328443943</v>
       </c>
       <c r="C7" t="n">
-        <v>6.942146604156552</v>
+        <v>7.263538704045673</v>
       </c>
       <c r="D7" t="n">
-        <v>7.525305686126209</v>
+        <v>6.703872275845878</v>
       </c>
       <c r="E7" t="n">
-        <v>16.51641644514479</v>
+        <v>15.51675030833549</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.287205660737413</v>
+        <v>1.717266441650279</v>
       </c>
       <c r="C8" t="n">
-        <v>4.580899702090495</v>
+        <v>8.453671757255199</v>
       </c>
       <c r="D8" t="n">
-        <v>5.836497651067768</v>
+        <v>7.083482285703681</v>
       </c>
       <c r="E8" t="n">
-        <v>11.70460301389568</v>
+        <v>17.25442048460916</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.646528256480973</v>
+        <v>1.869626179193682</v>
       </c>
       <c r="C9" t="n">
-        <v>5.542097400108328</v>
+        <v>9.791655344939857</v>
       </c>
       <c r="D9" t="n">
-        <v>6.360192292723993</v>
+        <v>7.4660230942982</v>
       </c>
       <c r="E9" t="n">
-        <v>13.54881794931329</v>
+        <v>19.12730461843174</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.035226504294814</v>
+        <v>1.14272487531216</v>
       </c>
       <c r="C10" t="n">
-        <v>6.649773810642726</v>
+        <v>7.17612411410023</v>
       </c>
       <c r="D10" t="n">
-        <v>6.912136764957184</v>
+        <v>5.876211613861114</v>
       </c>
       <c r="E10" t="n">
-        <v>15.59713707989472</v>
+        <v>14.1950606032735</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.444466844301264</v>
+        <v>1.089003640935774</v>
       </c>
       <c r="C11" t="n">
-        <v>7.854419085424041</v>
+        <v>7.679289447480805</v>
       </c>
       <c r="D11" t="n">
-        <v>7.561814908093971</v>
+        <v>5.717423740176234</v>
       </c>
       <c r="E11" t="n">
-        <v>17.86070083781928</v>
+        <v>14.48571682859281</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.864464243666804</v>
+        <v>1.191007227407018</v>
       </c>
       <c r="C12" t="n">
-        <v>9.174636975733472</v>
+        <v>9.135339102603336</v>
       </c>
       <c r="D12" t="n">
-        <v>8.064641767022254</v>
+        <v>6.133272432741099</v>
       </c>
       <c r="E12" t="n">
-        <v>20.10374298642253</v>
+        <v>16.45961876275145</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.280603587597344</v>
+        <v>0.9463458820316706</v>
       </c>
       <c r="C13" t="n">
-        <v>10.51705597110643</v>
+        <v>8.729307887080939</v>
       </c>
       <c r="D13" t="n">
-        <v>8.653072615643593</v>
+        <v>5.590110697889508</v>
       </c>
       <c r="E13" t="n">
-        <v>22.45073217434737</v>
+        <v>15.26576446700212</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.885181394125853</v>
+        <v>1.032798584867645</v>
       </c>
       <c r="C14" t="n">
-        <v>7.435128793434624</v>
+        <v>10.23520087314808</v>
       </c>
       <c r="D14" t="n">
-        <v>6.582098030691613</v>
+        <v>5.93037463470441</v>
       </c>
       <c r="E14" t="n">
-        <v>15.90240821825209</v>
+        <v>17.19837409272013</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.963367781292069</v>
+        <v>1.00501512483746</v>
       </c>
       <c r="C15" t="n">
-        <v>7.958930463558466</v>
+        <v>11.05480312656149</v>
       </c>
       <c r="D15" t="n">
-        <v>6.65401105002769</v>
+        <v>5.985470315866741</v>
       </c>
       <c r="E15" t="n">
-        <v>16.57630929487823</v>
+        <v>18.04528856726569</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.311171540475586</v>
+        <v>1.09805535476893</v>
       </c>
       <c r="C16" t="n">
-        <v>9.329293179054336</v>
+        <v>12.88288607420835</v>
       </c>
       <c r="D16" t="n">
-        <v>7.222344796016171</v>
+        <v>6.355785549908639</v>
       </c>
       <c r="E16" t="n">
-        <v>18.86280951554609</v>
+        <v>20.33672697888591</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.874450891718435</v>
+        <v>0.6532058350206154</v>
       </c>
       <c r="C17" t="n">
-        <v>8.583429995706906</v>
+        <v>9.635441383146661</v>
       </c>
       <c r="D17" t="n">
-        <v>6.775472875997108</v>
+        <v>5.27647175881378</v>
       </c>
       <c r="E17" t="n">
-        <v>17.23335376342245</v>
+        <v>15.56511897698106</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.168818123359799</v>
+        <v>0.5153586398673207</v>
       </c>
       <c r="C18" t="n">
-        <v>9.932881485102317</v>
+        <v>8.590793103488757</v>
       </c>
       <c r="D18" t="n">
-        <v>7.24529805734146</v>
+        <v>4.791694559933747</v>
       </c>
       <c r="E18" t="n">
-        <v>19.34699766580358</v>
+        <v>13.89784630328982</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.209599922994212</v>
+        <v>0.5989053694987243</v>
       </c>
       <c r="C19" t="n">
-        <v>10.53930704201557</v>
+        <v>10.61495070262779</v>
       </c>
       <c r="D19" t="n">
-        <v>7.381456646443451</v>
+        <v>5.287938571999383</v>
       </c>
       <c r="E19" t="n">
-        <v>20.13036361145323</v>
+        <v>16.50179464412589</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.499107503499553</v>
+        <v>0.6792123317061133</v>
       </c>
       <c r="C20" t="n">
-        <v>12.05380013797191</v>
+        <v>12.76477200791041</v>
       </c>
       <c r="D20" t="n">
-        <v>7.951616443161829</v>
+        <v>5.716707064352135</v>
       </c>
       <c r="E20" t="n">
-        <v>22.5045240846333</v>
+        <v>19.16069140396866</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.503409164375396</v>
+        <v>0.7518420268662923</v>
       </c>
       <c r="C21" t="n">
-        <v>8.820679145915189</v>
+        <v>15.01108929504345</v>
       </c>
       <c r="D21" t="n">
-        <v>6.6660570943588</v>
+        <v>6.181672594560466</v>
       </c>
       <c r="E21" t="n">
-        <v>16.99014540464939</v>
+        <v>21.94460391647021</v>
       </c>
     </row>
   </sheetData>
